--- a/lab-standards/WEAB-lab-standard.xlsx
+++ b/lab-standards/WEAB-lab-standard.xlsx
@@ -562,6 +562,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -575,6 +579,10 @@
 Workshop/ lab – 800 sft (75 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -644,7 +652,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -666,7 +676,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -688,7 +700,9 @@
       <c r="C18" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -710,7 +724,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -732,7 +748,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -754,7 +772,9 @@
       <c r="C21" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -776,7 +796,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -798,7 +820,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -820,7 +844,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -842,7 +868,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -864,7 +892,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -886,7 +916,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>9</v>
       </c>
@@ -908,7 +940,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>7</v>
       </c>
@@ -930,7 +964,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -952,7 +988,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>5</v>
       </c>
@@ -974,7 +1012,9 @@
       <c r="C31" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -996,7 +1036,9 @@
       <c r="C32" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>4</v>
       </c>
@@ -1018,7 +1060,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>4</v>
       </c>
@@ -1040,7 +1084,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -1186,6 +1232,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1199,6 +1249,10 @@
 Workshop/ lab – 800 sft (75 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1268,7 +1322,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -1290,7 +1346,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1312,7 +1370,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -1334,7 +1394,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -1356,7 +1418,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -1378,7 +1442,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -1400,7 +1466,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -1422,7 +1490,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -1444,7 +1514,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -1466,7 +1538,9 @@
       <c r="C25" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -1488,7 +1562,9 @@
       <c r="C26" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>3</v>
       </c>
@@ -1510,7 +1586,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>9</v>
       </c>
@@ -1532,7 +1610,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -1554,7 +1634,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>8</v>
       </c>
@@ -1576,7 +1658,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -1598,7 +1682,9 @@
       <c r="C31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -1620,7 +1706,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
@@ -1642,7 +1730,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -1664,7 +1754,9 @@
       <c r="C34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>5</v>
       </c>
@@ -1686,7 +1778,9 @@
       <c r="C35" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -1708,7 +1802,9 @@
       <c r="C36" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>4</v>
       </c>
@@ -1730,7 +1826,9 @@
       <c r="C37" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>4</v>
       </c>
@@ -1752,7 +1850,9 @@
       <c r="C38" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>3</v>
       </c>
@@ -1898,6 +1998,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1913,6 +2017,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1982,7 +2090,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -2004,7 +2114,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -2026,7 +2138,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -2048,7 +2162,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -2070,7 +2186,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -2092,7 +2210,9 @@
       <c r="C21" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -2114,7 +2234,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -2136,7 +2258,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -2282,6 +2406,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2297,6 +2425,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2366,7 +2498,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2388,7 +2522,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2410,7 +2546,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -2432,7 +2570,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -2454,7 +2594,9 @@
       <c r="C20" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>10</v>
       </c>
@@ -2476,7 +2618,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -2498,7 +2642,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -2520,7 +2666,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -2542,7 +2690,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -2564,7 +2714,9 @@
       <c r="C25" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -2586,7 +2738,9 @@
       <c r="C26" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -2732,6 +2886,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2746,6 +2904,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2815,7 +2977,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2837,7 +3001,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2859,7 +3025,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -2881,7 +3049,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -2903,7 +3073,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -2925,7 +3097,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -2947,7 +3121,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -2969,7 +3145,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -2991,7 +3169,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -3013,7 +3193,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>8</v>
       </c>
@@ -3035,7 +3217,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -3057,7 +3241,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -3079,7 +3265,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -3101,7 +3289,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -3123,7 +3313,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -3145,7 +3337,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>9</v>
       </c>
@@ -3167,7 +3361,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
@@ -3189,7 +3385,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -3335,6 +3533,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3347,6 +3549,10 @@
           <t>Classroom cum workshop – 500 - 600 sft (50-55 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3416,7 +3622,9 @@
       <c r="C16" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>10</v>
       </c>
@@ -3438,7 +3646,9 @@
       <c r="C17" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -3460,7 +3670,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -3482,7 +3694,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -3504,7 +3718,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -3526,7 +3742,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -3548,7 +3766,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -3570,7 +3790,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -3592,7 +3814,9 @@
       <c r="C24" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -3738,6 +3962,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3751,6 +3979,10 @@
 Workshop/ lab – 800 sft (75 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3820,7 +4052,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -3842,7 +4076,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -3864,7 +4100,9 @@
       <c r="C18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -3886,7 +4124,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -3908,7 +4148,9 @@
       <c r="C20" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -3930,7 +4172,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -3952,7 +4196,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -3974,7 +4220,9 @@
       <c r="C23" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -3996,7 +4244,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -4018,7 +4268,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -4040,7 +4292,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -4062,7 +4316,9 @@
       <c r="C27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>3</v>
       </c>
@@ -4084,7 +4340,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>7</v>
       </c>
@@ -4106,7 +4364,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -4128,7 +4388,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>3</v>
       </c>
@@ -4150,7 +4412,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>5</v>
       </c>
@@ -4172,7 +4436,9 @@
       <c r="C32" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>3</v>
       </c>
@@ -4194,7 +4460,9 @@
       <c r="C33" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
@@ -4216,7 +4484,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>3</v>
       </c>

--- a/lab-standards/WEAB-lab-standard.xlsx
+++ b/lab-standards/WEAB-lab-standard.xlsx
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Weighing Scale (Preferred capacity mm)</t>
+          <t>Weighing Scale (Preferred capacity 10 kg)</t>
         </is>
       </c>
       <c r="C33" s="9" t="n">

--- a/lab-standards/WEAB-lab-standard.xlsx
+++ b/lab-standards/WEAB-lab-standard.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -138,6 +138,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2347,7 +2353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -2406,10 +2412,6 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2425,10 +2427,6 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2487,16 +2485,16 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Computers/Laptop</t>
+          <t>Computer / Laptop (with relevant design software)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>0</v>
@@ -2511,12 +2509,12 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Projector &amp; Screen (HD quality, HDMI support, 3000+ lumens)</t>
+          <t>Multimedia Projector &amp; Screen (HD quality, HDMI support)</t>
         </is>
       </c>
       <c r="C17" s="9" t="n">
@@ -2535,7 +2533,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2559,22 +2557,22 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Mannequins/Dress Forms (Female and male standard sizes)</t>
+          <t>Single Needle Lock Stitch Machine (Industrial/Domestic)</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -2583,22 +2581,22 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Single needle lock stitch machine</t>
+          <t>Overlock Machine (3 or 4 threads)</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -2607,22 +2605,22 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Overlock machine</t>
+          <t>Embroidery Machine (Manual/Computerized)</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -2631,22 +2629,22 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Cutting table (60”x 50”)</t>
+          <t>Button Hole Machine</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -2655,12 +2653,12 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Electric iron</t>
+          <t>Button Stitch Machine</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
@@ -2679,22 +2677,22 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Electric steam iron with iron table</t>
+          <t>Cutting Table (Standard size: min. 5ft - 60”x50”)</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -2703,22 +2701,22 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Scissors (10”-12”)</t>
+          <t>Pattern Making &amp; Printing Table (Min 5ft)</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -2727,22 +2725,22 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Sewing tool box</t>
+          <t>Mannequins / Dress Forms (Male, Female, and Child standard sizes)</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -2750,57 +2748,249 @@
       </c>
       <c r="G26" s="9" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="27" ht="14.15" customHeight="1">
+      <c r="A27" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Electric Steam Iron with Ironing Table</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" s="9">
+        <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="14.15" customHeight="1">
+      <c r="A28" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Burner for Dyeing and Printing</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="9">
+        <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="9" t="n"/>
+    </row>
+    <row r="29" ht="14.15" customHeight="1">
+      <c r="A29" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Tracing Wheels</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="9">
+        <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="14.15" customHeight="1">
+      <c r="A30" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Sets of Pattern Making Curves (French curve, Hip curve, etc.)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" s="9">
+        <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="14.15" customHeight="1">
+      <c r="A31" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Fabric Cutting Scissors (10”-12”)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="9">
+        <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="14.15" customHeight="1">
+      <c r="A32" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Different Screen for Printing</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="9">
+        <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="9" t="n"/>
+    </row>
+    <row r="33" ht="14.15" customHeight="1">
+      <c r="A33" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Different Dices for Block Printing</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="9">
+        <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
+        <v/>
+      </c>
+      <c r="G33" s="9" t="n"/>
+    </row>
+    <row r="34" ht="14.15" customHeight="1">
+      <c r="A34" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Sewing Tool Box (Measuring tape, tailor’s chalk, needles, etc.)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="9">
+        <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="10">
-        <f>SUM(E16:E26)</f>
-        <v/>
-      </c>
-      <c r="F27" s="10">
-        <f>SUM(F16:F26)</f>
-        <v/>
-      </c>
-      <c r="G27" s="13" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="15">
+        <f>SUM(E16:E34)</f>
+        <v/>
+      </c>
+      <c r="F35" s="15">
+        <f>SUM(F16:F34)</f>
+        <v/>
+      </c>
+      <c r="G35" s="13" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="10">
-        <f>F27/E27*100</f>
-        <v/>
-      </c>
-      <c r="G28" s="13" t="n"/>
-    </row>
-    <row r="29" ht="9.75" customHeight="1"/>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="15">
+        <f>F35/E35*100</f>
+        <v/>
+      </c>
+      <c r="G36" s="13" t="n"/>
+    </row>
+    <row r="37" ht="9.75" customHeight="1"/>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
       </c>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="10">
-        <f>F28*30/100</f>
-        <v/>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="15">
+        <f>F36*30/100</f>
+        <v/>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -2808,14 +2998,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A30:E30"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A36:E36"/>
     <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
